--- a/data_extactor/batch_10_fa/trimmed/batch_0071_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0071_fa_trim.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>استحکام تنه | ثبات دست و بازو | چابکی دستی | هماهنگی چنداندامی | قدرت ایستا | دید نزدیک | استقامت عضلانی</t>
+          <t>قدرت تنه | ثبات دست و بازو | مهارت دستی | هماهنگی چند عضو | قدرت ایستا | بینایی نزدیک | استقامت</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین‌آلات و ادوات کشاورزی | تکنسین‌های کشاورزی | مدیران کشاورزی، دامپروری و سایر امور زراعی | کارگران دامداری، مرغداری و آبزی‌پروری | درجه‌بندی‌کنندگان و تفکیک‌کنندگان محصولات کشاورزی | کارگران فضای سبز و باغبانی | سم‌پاشان و متصدیان کنترل شیمیایی آفات گیاهی</t>
+          <t>اپراتورهای ماشین‌آلات و ادوات کشاورزی | تکنسین‌های کشاورزی | مدیران امور کشاورزی، دامپروری و شیلات | کارگران پرورش دام، طیور و آبزیان | کارگران درجه‌بندی و تفکیک محصولات کشاورزی | کارگران باغبانی، فضای سبز و نگهداری محوطه | سم‌پاشان و متصدیان کاربرد آفت‌کش‌های نباتی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | درک مطلب</t>
+          <t>تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>تولید و پردازش | زیست‌شناسی | مدیریت و امور اداری | زبان انگلیسی | مکانیک | تولید مواد غذایی | ریاضیات</t>
+          <t>تولید و فرآوری | زیست‌شناسی | مدیریت و اداره | زبان انگلیسی | مکانیک | تولید مواد غذایی | ریاضیات</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | ثبات دست و بازو | درک شفاهی | دید نزدیک | استحکام تنه | قدرت ایستا | چابکی دستی</t>
+          <t>حساسیت به مسئله | ثبات دست و بازو | درک شفاهی | بینایی نزدیک | قدرت تنه | قدرت ایستا | مهارت دستی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>تکنسین‌های کشاورزی | اصلاح‌نژادکنندگان و پرورش‌دهندگان دام | تیمارداران و مراقبان حیوانات | کارشناسان علوم دامی | مدیران کشاورزی، دامپروری و سایر امور زراعی | کارگران زراعت، نهالستان و گلخانه | قصابان و پاک‌کنندگان گوشت، مرغ و ماهی</t>
+          <t>تکنسین‌های کشاورزی | تکنسین‌ها و کارشناسان اصلاح نژاد و پرورش دام | مراقبان و نگهداران حیوانات | متخصصان علوم دامی | مدیران امور کشاورزی، دامپروری و شیلات | کارگران زراعت، نهالستان و گلخانه | برش‌کاران و پاک‌کنندگان گوشت، مرغ و آبزیان</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>تولید مواد غذایی | مکانیک | زیست‌شناسی | زبان انگلیسی | ایمنی و امنیت عمومی | شیمی | مدیریت و امور اداری</t>
+          <t>تولید مواد غذایی | مکانیک | زیست‌شناسی | زبان انگلیسی | ایمنی و امنیت عمومی | شیمی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>چابکی دستی | ثبات دست و بازو | هماهنگی چنداندامی | دقت کنترل | قدرت ایستا | استحکام تنه | دید نزدیک</t>
+          <t>مهارت دستی | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>کارگران زراعت، نهالستان و گلخانه | کارگران دامداری، مرغداری و آبزی‌پروری | اپراتورهای ماشین‌آلات و ادوات کشاورزی | درجه‌بندی‌کنندگان و تفکیک‌کنندگان محصولات کشاورزی | کارگران فضای سبز و باغبانی | سم‌پاشان و متصدیان کنترل شیمیایی آفات گیاهی | تکنسین‌های کشاورزی</t>
+          <t>کارگران زراعت، نهالستان و گلخانه | کارگران پرورش دام، طیور و آبزیان | اپراتورهای ماشین‌آلات و ادوات کشاورزی | کارگران درجه‌بندی و تفکیک محصولات کشاورزی | کارگران باغبانی، فضای سبز و نگهداری محوطه | سم‌پاشان و متصدیان کاربرد آفت‌کش‌های نباتی | تکنسین‌های کشاورزی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -684,12 +684,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>جغرافیا | مکانیک | حقوق و مقررات دولتی | خدمات مشتریان و خدمات فردی | زیست‌شناسی | فروش و بازاریابی</t>
+          <t>جغرافیا | مکانیک | قانون و دولت | خدمات مشتری و شخصی | زیست‌شناسی | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>جهت‌یابی فضایی | دید دور | قدرت ایستا | استحکام تنه | حساسیت به مسئله | چابکی دستی | هماهنگی چنداندامی</t>
+          <t>جهت‌گیری فضایی | بینایی دور | قدرت ایستا | قدرت تنه | حساسیت به مسئله | مهارت دستی | هماهنگی چند عضو</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>کاپیتان‌ها، افسران اول و ناوبُران شناورهای دریایی | کارگران دامداری، مرغداری و آبزی‌پروری | سرپرستان رده‌اول کارگران کشاورزی، صیادی و جنگل‌داری | محیط‌بانان و مأموران حفاظت شیلات و شکاربانی | قصابان و پاک‌کنندگان گوشت، مرغ و ماهی | قایق‌رانان شناورهای موتوری | ملوانان و روغن‌کاران موتورخانه شناور</t>
+          <t>کاپیتان‌ها، افسران اول و راهنمایان شناورهای دریایی | کارگران پرورش دام، طیور و آبزیان | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | محیط‌بانان و ماموران حفاظت شیلات و حیات وحش | برش‌کاران و پاک‌کنندگان گوشت، مرغ و آبزیان | قایقرانان قایق‌های موتوری | ملوانان و روغن‌کاران شناورهای دریایی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | یادگیری فعال | سخن گفتن | شنیدن فعال | درک مطلب</t>
+          <t>تفکر انتقادی | نظارت | یادگیری فعال | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | جغرافیا | زیست‌شناسی</t>
+          <t>ایمنی و امنیت عمومی | زبان انگلیسی | خدمات مشتری و شخصی | مدیریت و اداره | جغرافیا | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | قدرت ایستا | دید دور | استقامت عضلانی | استحکام تنه | هماهنگی چنداندامی</t>
+          <t>حساسیت به مسئله | درک شفاهی | قدرت ایستا | بینایی دور | استقامت | قدرت تنه | هماهنگی چند عضو</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کارشناسان حفاظت از خاک و منابع طبیعی | درخت‌اندازان و چوب‌بُران جنگل | سرپرستان رده‌اول کارگران کشاورزی، صیادی و جنگل‌داری | محیط‌بانان و مأموران حفاظت شیلات و شکاربانی | تکنسین‌های جنگل‌داری و حفاظت از منابع طبیعی | کارگران فضای سبز و باغبانی | هرس‌کاران و پیرایندگان درختان</t>
+          <t>دانشمندان حفاظت از منابع طبیعی | درخت‌اندازان و چوب‌بُران جنگل | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | محیط‌بانان و ماموران حفاظت شیلات و حیات وحش | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | کارگران باغبانی، فضای سبز و نگهداری محوطه | هرس‌کنندگان و پیرایندگان درختان</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>مکانیک | ایمنی و امنیت عمومی | زیست‌شناسی | زبان انگلیسی | ریاضیات | تولید و پردازش</t>
+          <t>مکانیک | ایمنی و امنیت عمومی | زیست‌شناسی | زبان انگلیسی | ریاضیات | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>زمان واکنش | هماهنگی چنداندامی | دقت کنترل | قدرت ایستا | ادراک عمق | استقامت عضلانی | استحکام تنه</t>
+          <t>زمان عکس‌العمل | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | درک عمق | استقامت | قدرت تنه</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>سرپرستان رده‌اول کارگران کشاورزی، صیادی و جنگل‌داری | تکنسین‌های جنگل‌داری و حفاظت از منابع طبیعی | کارگران جنگل‌داری و حفاظت از منابع طبیعی | ارزیابان، ابعادبرداران و درجه‌بندی‌کنندگان الوار | اپراتورهای ماشین‌آلات مکانیزه چوب‌بری و جنگل‌داری | تنظیم‌کنندگان و اپراتورهای ماشین‌های اره‌کشی چوب | هرس‌کاران و پیرایندگان درختان</t>
+          <t>سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | کارگران جنگل‌داری و حفاظت از منابع طبیعی | ارزیابان، ابعادبرداران و درجه‌بندی‌کنندگان الوار | اپراتورهای ماشین‌آلات چوب‌بری و چوب‌کشی | تنظیم‌کنندگان، متصدیان و اپراتورهای اره‌ چوب‌بری | هرس‌کنندگان و پیرایندگان درختان</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال</t>
+          <t>نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>مکانیک | ایمنی و امنیت عمومی | تولید و پردازش</t>
+          <t>مکانیک | ایمنی و امنیت عمومی | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دقت کنترل | زمان واکنش | هماهنگی چنداندامی | ثبات دست و بازو | ادراک عمق | دید دور | چابکی دستی</t>
+          <t>دقت کنترل | زمان عکس‌العمل | هماهنگی چند عضو | ثبات دست و بازو | درک عمق | بینایی دور | مهارت دستی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین‌آلات و ادوات کشاورزی | درخت‌اندازان و چوب‌بُران جنگل | اپراتورهای بالابر و وینچ | رانندگان لیفتراک و تراکتورهای صنعتی | ارزیابان، ابعادبرداران و درجه‌بندی‌کنندگان الوار | اپراتورهای ماشین‌آلات راه‌سازی و تجهیزات عمرانی | تنظیم‌کنندگان و اپراتورهای ماشین‌های اره‌کشی چوب</t>
+          <t>اپراتورهای ماشین‌آلات و ادوات کشاورزی | درخت‌اندازان و چوب‌بُران جنگل | اپراتورهای بالابر و وینچ | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | ارزیابان، ابعادبرداران و درجه‌بندی‌کنندگان الوار | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | تنظیم‌کنندگان، متصدیان و اپراتورهای اره‌ چوب‌بری</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | سخن گفتن | یادگیری فعال | نگارش | نظارت</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | یادگیری فعال | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>تولید و پردازش | ریاضیات | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری</t>
+          <t>تولید و فرآوری | ریاضیات | خدمات مشتری و شخصی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | حساسیت به مسئله | درک شفاهی | استدلال قیاسی | انعطاف‌پذیری طبقه‌بندی | دید دور | کار با اعداد</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | درک شفاهی | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | بینایی دور | توانایی عددی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌آلات برش و اسلایس چوب | درخت‌اندازان و چوب‌بُران جنگل | درجه‌بندی‌کنندگان و تفکیک‌کنندگان محصولات کشاورزی | بازرسان، آزمون‌گران، تفکیک‌کنندگان، نمونه‌برداران و متصدیان توزین | اپراتورهای ماشین‌آلات چوب‌بری و چوب‌کشی | کارمندان برنامه‌ریزی، تولید و تسریع سفارش‌ها | متصدیان توزین، ابعادبرداری، کنترل و ثبت اطلاعات بار</t>
+          <t>تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | درخت‌اندازان و چوب‌بُران جنگل | کارگران درجه‌بندی و تفکیک محصولات کشاورزی | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | اپراتورهای ماشین‌آلات چوب‌بری و چوب‌کشی | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | متصدیان توزین، سنجش، بازرسی و نمونه‌برداری ثبت اسناد</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مکانیک | ایمنی و امنیت عمومی | زبان انگلیسی | تولید و پردازش | زیست‌شناسی | حمل‌ونقل | ریاضیات</t>
+          <t>مکانیک | ایمنی و امنیت عمومی | زبان انگلیسی | تولید و فرآوری | زیست‌شناسی | حمل و نقل | ریاضیات</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>چابکی دستی | ثبات دست و بازو | هماهنگی چنداندامی | دقت کنترل | قدرت ایستا | استحکام تنه | دید نزدیک</t>
+          <t>مهارت دستی | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>درخت‌اندازان و چوب‌بُران جنگل | اپراتورهای ماشین‌آلات چوب‌بری و چوب‌کشی | ارزیابان، ابعادبرداران و درجه‌بندی‌کنندگان الوار | کارگران جنگل‌داری و حفاظت از منابع طبیعی | تکنسین‌های جنگل‌داری و حفاظت از منابع طبیعی | هرس‌کاران و پیرایندگان درختان | کارگران حمل، بارگیری و جابه‌جایی دستی بار</t>
+          <t>درخت‌اندازان و چوب‌بُران جنگل | اپراتورهای ماشین‌آلات چوب‌بری و چوب‌کشی | ارزیابان، ابعادبرداران و درجه‌بندی‌کنندگان الوار | کارگران جنگل‌داری و حفاظت از منابع طبیعی | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | هرس‌کنندگان و پیرایندگان درختان | کارگران جابه‌جایی دستی بار، کالا و مصالح</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | راهبردهای یادگیری | یادگیری فعال | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | راهبردهای یادگیری | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | ساختمان و سازه | مکانیک | طراحی | ایمنی و امنیت عمومی | ریاضیات | مهندسی و فناوری</t>
+          <t>مدیریت و اداره | ساختمان و ساخت‌وساز | مکانیک | طراحی | ایمنی و امنیت عمومی | ریاضیات | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | استدلال قیاسی | درک کتبی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | استدلال قیاسی | درک کتبی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>کاردان‌ها و تکنسین‌های مهندسی عمران | مدیران پروژه‌های ساختمانی و عمرانی | بازرسان فنی ساختمان و سازه | برق‌کاران صنعتی و ساختمانی | سرپرستان رده‌اول تعمیرکاران، نصابان و مکانیک‌ها | سرپرستان رده‌اول کارگران خطوط تولید و عملیات | مدیران اجرایی و مدیران عملیات</t>
+          <t>کارشناسان و تکنسین‌های مهندسی عمران | مدیران پروژه‌های ساختمانی | بازرسان ساخت‌وساز و ساختمان | برق‌کاران | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده اول کارگران تولید و عملیات | مدیران کل و مدیران عملیات</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
